--- a/src/main/resources/PaymentRequest_Field_Values.xlsx
+++ b/src/main/resources/PaymentRequest_Field_Values.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4505"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Product\govgrants-product-automation\src\main\resources\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A66CEE4-C343-4C61-9D41-E8B16F7C0E8E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Adhoc Reimbursement Creation" sheetId="1" r:id="rId1"/>
@@ -14,8 +20,8 @@
     <sheet name="No Program Income_Edition" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -23,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="22">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -58,18 +64,9 @@
     <t>Checked</t>
   </si>
   <si>
-    <t>CheckNumber__c</t>
-  </si>
-  <si>
     <t>VoucherNumber__c</t>
   </si>
   <si>
-    <t>PaidDate__c</t>
-  </si>
-  <si>
-    <t>PaymentReference__c</t>
-  </si>
-  <si>
     <t>Nil</t>
   </si>
   <si>
@@ -77,19 +74,46 @@
   </si>
   <si>
     <t xml:space="preserve">Automation Payment Request </t>
+  </si>
+  <si>
+    <t>fieldYTDEarnedAmount__c</t>
+  </si>
+  <si>
+    <t>fieldTermsAgreement__c</t>
+  </si>
+  <si>
+    <t>fieldReceiptsUploaded__c</t>
+  </si>
+  <si>
+    <t>fieldCheckNumber__c</t>
+  </si>
+  <si>
+    <t>fieldVoucherNumber__c</t>
+  </si>
+  <si>
+    <t>fieldPaidDate__c</t>
+  </si>
+  <si>
+    <t>fieldPaymentReference__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF222222"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -112,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -120,6 +144,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -426,22 +451,22 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -452,7 +477,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -460,7 +485,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -469,16 +494,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.28515625" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -489,18 +514,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>78954</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -511,7 +536,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -522,7 +547,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -539,15 +564,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -558,34 +583,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
-        <v>5</v>
+      <c r="B2" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="C2">
         <v>1000</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
-        <v>7</v>
+      <c r="B3" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
-        <v>9</v>
+      <c r="B4" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -598,15 +623,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -617,48 +642,48 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C2">
         <v>6789678654</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C3">
         <v>5678</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C4">
         <v>-5</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -668,15 +693,15 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
     <col min="2" max="2" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -687,7 +712,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -698,7 +723,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>

--- a/src/main/resources/PaymentRequest_Field_Values.xlsx
+++ b/src/main/resources/PaymentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_New_Clone\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Project\ProdLWC_Mine\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB51AE2E-4E15-4AB1-A932-275CAA85AC51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B921D1E2-8A85-4205-B4BA-D8967EE67093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Adhoc Reimbursement Creation" sheetId="1" r:id="rId1"/>
@@ -340,9 +340,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -380,7 +380,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -486,7 +486,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -628,7 +628,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -745,7 +745,7 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="34.28515625" customWidth="1"/>
+    <col min="2" max="2" width="38.5703125" customWidth="1"/>
     <col min="3" max="3" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>

--- a/src/main/resources/PaymentRequest_Field_Values.xlsx
+++ b/src/main/resources/PaymentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_New_Clone\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB51AE2E-4E15-4AB1-A932-275CAA85AC51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF9E25FE-F633-4B22-A8F9-F5D5E4415897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Adhoc Reimbursement Creation" sheetId="1" r:id="rId1"/>
@@ -86,180 +86,51 @@
     <t xml:space="preserve">Automation Payment Request </t>
   </si>
   <si>
-    <t>fieldTypeOfRequest__c</t>
-  </si>
-  <si>
     <t>Final</t>
   </si>
   <si>
-    <t>fieldBasisOfRequest__c</t>
-  </si>
-  <si>
     <t>Cash</t>
   </si>
   <si>
-    <t>fieldFederalAgencySF428__c</t>
-  </si>
-  <si>
     <t>TEST12345</t>
   </si>
   <si>
-    <t>fieldFederalAwardIdentifier__c</t>
-  </si>
-  <si>
-    <t>fieldPartialPaymentRequest__c</t>
-  </si>
-  <si>
-    <t>fieldFinancialAssistance__c</t>
-  </si>
-  <si>
-    <t>fieldPeriodStartDate__c</t>
-  </si>
-  <si>
-    <t>fieldPeriodEndDate__c</t>
-  </si>
-  <si>
-    <t>fieldRecipientOrganizationNameSF428__c</t>
-  </si>
-  <si>
     <t>TEST Organization</t>
   </si>
   <si>
-    <t>fieldStreet1SF428__c</t>
-  </si>
-  <si>
-    <t>fieldStreet2SF428__c</t>
-  </si>
-  <si>
     <t>Street 2</t>
   </si>
   <si>
-    <t>fieldCitySF428__c</t>
-  </si>
-  <si>
-    <t>fieldCountySF428__c</t>
-  </si>
-  <si>
     <t>NY</t>
   </si>
   <si>
-    <t>fieldStateSf428__c</t>
-  </si>
-  <si>
-    <t>fieldProvinceSF428__c</t>
-  </si>
-  <si>
-    <t>fieldCountrySF428__c</t>
-  </si>
-  <si>
     <t>USA: UNITED STATES</t>
   </si>
   <si>
-    <t>fieldZipPostalCodeSF428__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeOrganizationName__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeStreet1__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeStreet2__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeCity__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeCounty__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeState__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeProvince__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeCountry__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeZipCode__c</t>
-  </si>
-  <si>
-    <t>fieldPrograms__c</t>
-  </si>
-  <si>
-    <t>fieldFunctions__c</t>
-  </si>
-  <si>
-    <t>fieldActivities__c</t>
-  </si>
-  <si>
-    <t>fieldAcquiredDate__c</t>
-  </si>
-  <si>
-    <t>fieldEstimatedFederalCashOutlays__c</t>
-  </si>
-  <si>
-    <t>fieldEstimatedBalanceofFederalCashonHand__c</t>
-  </si>
-  <si>
-    <t>fieldAcknowledgementSF428__c</t>
-  </si>
-  <si>
     <t>checked</t>
   </si>
   <si>
-    <t>fieldSubmittedBySF428__c</t>
-  </si>
-  <si>
     <t>John Mathews</t>
   </si>
   <si>
-    <t>fieldSubmittedOn__c</t>
-  </si>
-  <si>
-    <t>fieldPrefix__c</t>
-  </si>
-  <si>
     <t>Mr.</t>
   </si>
   <si>
-    <t>fieldFirstNameSF428__c</t>
-  </si>
-  <si>
     <t>John</t>
   </si>
   <si>
-    <t>fieldMiddleNameSF428__c</t>
-  </si>
-  <si>
     <t>Andrew</t>
   </si>
   <si>
-    <t>fieldLastNameSF428__c</t>
-  </si>
-  <si>
     <t>Mathews</t>
   </si>
   <si>
-    <t>fieldSuffix__c</t>
-  </si>
-  <si>
     <t>Jr.</t>
   </si>
   <si>
-    <t>fieldTitleSF429__c</t>
-  </si>
-  <si>
     <t>Associate</t>
   </si>
   <si>
-    <t>fieldTelephone__c</t>
-  </si>
-  <si>
-    <t>fieldAgencyCommentsSF428__c</t>
-  </si>
-  <si>
     <t>Automation Test</t>
   </si>
   <si>
@@ -267,6 +138,135 @@
   </si>
   <si>
     <t>NY: New York</t>
+  </si>
+  <si>
+    <t>TypeOfRequest__c</t>
+  </si>
+  <si>
+    <t>BasisOfRequest__c</t>
+  </si>
+  <si>
+    <t>FederalAgencySF428__c</t>
+  </si>
+  <si>
+    <t>FederalAwardIdentifier__c</t>
+  </si>
+  <si>
+    <t>PartialPaymentRequest__c</t>
+  </si>
+  <si>
+    <t>FinancialAssistance__c</t>
+  </si>
+  <si>
+    <t>PeriodStartDate__c</t>
+  </si>
+  <si>
+    <t>PeriodEndDate__c</t>
+  </si>
+  <si>
+    <t>RecipientOrganizationNameSF428__c</t>
+  </si>
+  <si>
+    <t>Street1SF428__c</t>
+  </si>
+  <si>
+    <t>Street2SF428__c</t>
+  </si>
+  <si>
+    <t>CitySF428__c</t>
+  </si>
+  <si>
+    <t>CountySF428__c</t>
+  </si>
+  <si>
+    <t>StateSf428__c</t>
+  </si>
+  <si>
+    <t>ProvinceSF428__c</t>
+  </si>
+  <si>
+    <t>CountrySF428__c</t>
+  </si>
+  <si>
+    <t>ZipPostalCodeSF428__c</t>
+  </si>
+  <si>
+    <t>PayeeOrganizationName__c</t>
+  </si>
+  <si>
+    <t>PayeeStreet1__c</t>
+  </si>
+  <si>
+    <t>PayeeStreet2__c</t>
+  </si>
+  <si>
+    <t>PayeeCity__c</t>
+  </si>
+  <si>
+    <t>PayeeCounty__c</t>
+  </si>
+  <si>
+    <t>PayeeState__c</t>
+  </si>
+  <si>
+    <t>PayeeProvince__c</t>
+  </si>
+  <si>
+    <t>PayeeCountry__c</t>
+  </si>
+  <si>
+    <t>PayeeZipCode__c</t>
+  </si>
+  <si>
+    <t>Programs__c</t>
+  </si>
+  <si>
+    <t>Functions__c</t>
+  </si>
+  <si>
+    <t>Activities__c</t>
+  </si>
+  <si>
+    <t>AcquiredDate__c</t>
+  </si>
+  <si>
+    <t>EstimatedFederalCashOutlays__c</t>
+  </si>
+  <si>
+    <t>EstimatedBalanceofFederalCashonHand__c</t>
+  </si>
+  <si>
+    <t>AcknowledgementSF428__c</t>
+  </si>
+  <si>
+    <t>SubmittedBySF428__c</t>
+  </si>
+  <si>
+    <t>SubmittedOn__c</t>
+  </si>
+  <si>
+    <t>Prefix__c</t>
+  </si>
+  <si>
+    <t>FirstNameSF428__c</t>
+  </si>
+  <si>
+    <t>MiddleNameSF428__c</t>
+  </si>
+  <si>
+    <t>LastNameSF428__c</t>
+  </si>
+  <si>
+    <t>Suffix__c</t>
+  </si>
+  <si>
+    <t>TitleSF429__c</t>
+  </si>
+  <si>
+    <t>Telephone__c</t>
+  </si>
+  <si>
+    <t>AgencyCommentsSF428__c</t>
   </si>
 </sst>
 </file>
@@ -340,9 +340,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -380,7 +380,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -486,7 +486,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -628,7 +628,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -637,13 +637,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -654,7 +654,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -673,14 +673,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" customWidth="1"/>
+    <col min="1" max="1" width="10.26953125" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" customWidth="1"/>
+    <col min="3" max="3" width="23.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -691,7 +691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -702,7 +702,7 @@
         <v>78954</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -713,7 +713,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -724,7 +724,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -743,13 +743,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="34.28515625" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" customWidth="1"/>
+    <col min="2" max="2" width="34.26953125" customWidth="1"/>
+    <col min="3" max="3" width="16.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -760,7 +760,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -771,7 +771,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -782,7 +782,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -802,13 +802,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -819,7 +819,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -830,7 +830,7 @@
         <v>6789678654</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -841,7 +841,7 @@
         <v>5678</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -852,7 +852,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -872,14 +872,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="12.26953125" customWidth="1"/>
+    <col min="2" max="2" width="20.81640625" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -890,7 +890,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -901,7 +901,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -920,13 +920,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A20A769E-7CDB-4643-B4E8-C9AF9D26E6C8}">
   <dimension ref="A1:C44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.1796875" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -937,477 +937,477 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C5" s="3">
         <v>123456789</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C6" s="3">
         <v>2121323223</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C7" s="3">
         <v>2121323223</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="C8" s="3">
         <v>365</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="C9" s="3">
         <v>730</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C11" s="3">
         <v>123</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
       <c r="B13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C20" s="3">
         <v>123</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>3</v>
       </c>
       <c r="B25" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="C28" s="3">
         <v>12345</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>3</v>
       </c>
       <c r="B29" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C29" s="3">
         <v>12345</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>3</v>
       </c>
       <c r="B30" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C30" s="3">
         <v>12345</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>3</v>
       </c>
       <c r="B31" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C31" s="3">
         <v>570</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C32" s="3">
         <v>12345</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>3</v>
       </c>
       <c r="B33" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C33" s="3">
         <v>12345</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C35" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C36" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>3</v>
       </c>
       <c r="B38" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>3</v>
       </c>
       <c r="B39" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>3</v>
       </c>
       <c r="B40" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>3</v>
       </c>
       <c r="B41" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>3</v>
       </c>
       <c r="B42" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>3</v>
       </c>
       <c r="B43" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C43" s="3">
         <v>2122342342</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/PaymentRequest_Field_Values.xlsx
+++ b/src/main/resources/PaymentRequest_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF9E25FE-F633-4B22-A8F9-F5D5E4415897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9385A66A-8F46-44E9-9CB1-D1C4AC0EA5AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="80">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -267,6 +267,9 @@
   </si>
   <si>
     <t>AgencyCommentsSF428__c</t>
+  </si>
+  <si>
+    <t>FL: Florida</t>
   </si>
 </sst>
 </file>
@@ -1187,7 +1190,7 @@
         <v>58</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">

--- a/src/main/resources/PaymentRequest_Field_Values.xlsx
+++ b/src/main/resources/PaymentRequest_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Project\ProdLWC_Mine\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9385A66A-8F46-44E9-9CB1-D1C4AC0EA5AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B921D1E2-8A85-4205-B4BA-D8967EE67093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Adhoc Reimbursement Creation" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="79">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -86,51 +86,180 @@
     <t xml:space="preserve">Automation Payment Request </t>
   </si>
   <si>
+    <t>fieldTypeOfRequest__c</t>
+  </si>
+  <si>
     <t>Final</t>
   </si>
   <si>
+    <t>fieldBasisOfRequest__c</t>
+  </si>
+  <si>
     <t>Cash</t>
   </si>
   <si>
+    <t>fieldFederalAgencySF428__c</t>
+  </si>
+  <si>
     <t>TEST12345</t>
   </si>
   <si>
+    <t>fieldFederalAwardIdentifier__c</t>
+  </si>
+  <si>
+    <t>fieldPartialPaymentRequest__c</t>
+  </si>
+  <si>
+    <t>fieldFinancialAssistance__c</t>
+  </si>
+  <si>
+    <t>fieldPeriodStartDate__c</t>
+  </si>
+  <si>
+    <t>fieldPeriodEndDate__c</t>
+  </si>
+  <si>
+    <t>fieldRecipientOrganizationNameSF428__c</t>
+  </si>
+  <si>
     <t>TEST Organization</t>
   </si>
   <si>
+    <t>fieldStreet1SF428__c</t>
+  </si>
+  <si>
+    <t>fieldStreet2SF428__c</t>
+  </si>
+  <si>
     <t>Street 2</t>
   </si>
   <si>
+    <t>fieldCitySF428__c</t>
+  </si>
+  <si>
+    <t>fieldCountySF428__c</t>
+  </si>
+  <si>
     <t>NY</t>
   </si>
   <si>
+    <t>fieldStateSf428__c</t>
+  </si>
+  <si>
+    <t>fieldProvinceSF428__c</t>
+  </si>
+  <si>
+    <t>fieldCountrySF428__c</t>
+  </si>
+  <si>
     <t>USA: UNITED STATES</t>
   </si>
   <si>
+    <t>fieldZipPostalCodeSF428__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeOrganizationName__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeStreet1__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeStreet2__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeCity__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeCounty__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeState__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeProvince__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeCountry__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeZipCode__c</t>
+  </si>
+  <si>
+    <t>fieldPrograms__c</t>
+  </si>
+  <si>
+    <t>fieldFunctions__c</t>
+  </si>
+  <si>
+    <t>fieldActivities__c</t>
+  </si>
+  <si>
+    <t>fieldAcquiredDate__c</t>
+  </si>
+  <si>
+    <t>fieldEstimatedFederalCashOutlays__c</t>
+  </si>
+  <si>
+    <t>fieldEstimatedBalanceofFederalCashonHand__c</t>
+  </si>
+  <si>
+    <t>fieldAcknowledgementSF428__c</t>
+  </si>
+  <si>
     <t>checked</t>
   </si>
   <si>
+    <t>fieldSubmittedBySF428__c</t>
+  </si>
+  <si>
     <t>John Mathews</t>
   </si>
   <si>
+    <t>fieldSubmittedOn__c</t>
+  </si>
+  <si>
+    <t>fieldPrefix__c</t>
+  </si>
+  <si>
     <t>Mr.</t>
   </si>
   <si>
+    <t>fieldFirstNameSF428__c</t>
+  </si>
+  <si>
     <t>John</t>
   </si>
   <si>
+    <t>fieldMiddleNameSF428__c</t>
+  </si>
+  <si>
     <t>Andrew</t>
   </si>
   <si>
+    <t>fieldLastNameSF428__c</t>
+  </si>
+  <si>
     <t>Mathews</t>
   </si>
   <si>
+    <t>fieldSuffix__c</t>
+  </si>
+  <si>
     <t>Jr.</t>
   </si>
   <si>
+    <t>fieldTitleSF429__c</t>
+  </si>
+  <si>
     <t>Associate</t>
   </si>
   <si>
+    <t>fieldTelephone__c</t>
+  </si>
+  <si>
+    <t>fieldAgencyCommentsSF428__c</t>
+  </si>
+  <si>
     <t>Automation Test</t>
   </si>
   <si>
@@ -138,138 +267,6 @@
   </si>
   <si>
     <t>NY: New York</t>
-  </si>
-  <si>
-    <t>TypeOfRequest__c</t>
-  </si>
-  <si>
-    <t>BasisOfRequest__c</t>
-  </si>
-  <si>
-    <t>FederalAgencySF428__c</t>
-  </si>
-  <si>
-    <t>FederalAwardIdentifier__c</t>
-  </si>
-  <si>
-    <t>PartialPaymentRequest__c</t>
-  </si>
-  <si>
-    <t>FinancialAssistance__c</t>
-  </si>
-  <si>
-    <t>PeriodStartDate__c</t>
-  </si>
-  <si>
-    <t>PeriodEndDate__c</t>
-  </si>
-  <si>
-    <t>RecipientOrganizationNameSF428__c</t>
-  </si>
-  <si>
-    <t>Street1SF428__c</t>
-  </si>
-  <si>
-    <t>Street2SF428__c</t>
-  </si>
-  <si>
-    <t>CitySF428__c</t>
-  </si>
-  <si>
-    <t>CountySF428__c</t>
-  </si>
-  <si>
-    <t>StateSf428__c</t>
-  </si>
-  <si>
-    <t>ProvinceSF428__c</t>
-  </si>
-  <si>
-    <t>CountrySF428__c</t>
-  </si>
-  <si>
-    <t>ZipPostalCodeSF428__c</t>
-  </si>
-  <si>
-    <t>PayeeOrganizationName__c</t>
-  </si>
-  <si>
-    <t>PayeeStreet1__c</t>
-  </si>
-  <si>
-    <t>PayeeStreet2__c</t>
-  </si>
-  <si>
-    <t>PayeeCity__c</t>
-  </si>
-  <si>
-    <t>PayeeCounty__c</t>
-  </si>
-  <si>
-    <t>PayeeState__c</t>
-  </si>
-  <si>
-    <t>PayeeProvince__c</t>
-  </si>
-  <si>
-    <t>PayeeCountry__c</t>
-  </si>
-  <si>
-    <t>PayeeZipCode__c</t>
-  </si>
-  <si>
-    <t>Programs__c</t>
-  </si>
-  <si>
-    <t>Functions__c</t>
-  </si>
-  <si>
-    <t>Activities__c</t>
-  </si>
-  <si>
-    <t>AcquiredDate__c</t>
-  </si>
-  <si>
-    <t>EstimatedFederalCashOutlays__c</t>
-  </si>
-  <si>
-    <t>EstimatedBalanceofFederalCashonHand__c</t>
-  </si>
-  <si>
-    <t>AcknowledgementSF428__c</t>
-  </si>
-  <si>
-    <t>SubmittedBySF428__c</t>
-  </si>
-  <si>
-    <t>SubmittedOn__c</t>
-  </si>
-  <si>
-    <t>Prefix__c</t>
-  </si>
-  <si>
-    <t>FirstNameSF428__c</t>
-  </si>
-  <si>
-    <t>MiddleNameSF428__c</t>
-  </si>
-  <si>
-    <t>LastNameSF428__c</t>
-  </si>
-  <si>
-    <t>Suffix__c</t>
-  </si>
-  <si>
-    <t>TitleSF429__c</t>
-  </si>
-  <si>
-    <t>Telephone__c</t>
-  </si>
-  <si>
-    <t>AgencyCommentsSF428__c</t>
-  </si>
-  <si>
-    <t>FL: Florida</t>
   </si>
 </sst>
 </file>
@@ -640,13 +637,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -657,7 +654,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -676,14 +673,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.26953125" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="23.81640625" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -694,7 +691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -705,7 +702,7 @@
         <v>78954</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -716,7 +713,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -727,7 +724,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -746,13 +743,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="34.26953125" customWidth="1"/>
-    <col min="3" max="3" width="16.54296875" customWidth="1"/>
+    <col min="2" max="2" width="38.5703125" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -763,7 +760,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -774,7 +771,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -785,7 +782,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -805,13 +802,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="19.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7265625" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -822,7 +819,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -833,7 +830,7 @@
         <v>6789678654</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -844,7 +841,7 @@
         <v>5678</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -855,7 +852,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -875,14 +872,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.26953125" customWidth="1"/>
-    <col min="2" max="2" width="20.81640625" customWidth="1"/>
+    <col min="1" max="1" width="12.28515625" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -893,7 +890,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -904,7 +901,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -923,13 +920,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A20A769E-7CDB-4643-B4E8-C9AF9D26E6C8}">
   <dimension ref="A1:C44"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -940,477 +937,477 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3">
         <v>123456789</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C6" s="3">
         <v>2121323223</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C7" s="3">
         <v>2121323223</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C8" s="3">
         <v>365</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C9" s="3">
         <v>730</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C11" s="3">
         <v>123</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" t="s">
-        <v>48</v>
-      </c>
       <c r="C14" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C20" s="3">
         <v>123</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>3</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C28" s="3">
         <v>12345</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>3</v>
       </c>
       <c r="B29" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C29" s="3">
         <v>12345</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>3</v>
       </c>
       <c r="B30" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C30" s="3">
         <v>12345</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>3</v>
       </c>
       <c r="B31" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C31" s="3">
         <v>570</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C32" s="3">
         <v>12345</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>3</v>
       </c>
       <c r="B33" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C33" s="3">
         <v>12345</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C35" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C36" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>3</v>
       </c>
       <c r="B37" t="s">
+        <v>62</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>3</v>
+      </c>
+      <c r="B38" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>3</v>
+      </c>
+      <c r="B39" t="s">
+        <v>66</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>3</v>
+      </c>
+      <c r="B40" t="s">
+        <v>68</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>3</v>
+      </c>
+      <c r="B41" t="s">
+        <v>70</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>3</v>
-      </c>
-      <c r="B38" t="s">
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>3</v>
+      </c>
+      <c r="B42" t="s">
         <v>72</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>3</v>
-      </c>
-      <c r="B39" t="s">
+      <c r="C42" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>3</v>
-      </c>
-      <c r="B40" t="s">
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>3</v>
+      </c>
+      <c r="B43" t="s">
         <v>74</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>3</v>
-      </c>
-      <c r="B41" t="s">
-        <v>75</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>3</v>
-      </c>
-      <c r="B42" t="s">
-        <v>76</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>3</v>
-      </c>
-      <c r="B43" t="s">
-        <v>77</v>
       </c>
       <c r="C43" s="3">
         <v>2122342342</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/PaymentRequest_Field_Values.xlsx
+++ b/src/main/resources/PaymentRequest_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Project\ProdLWC_Mine\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B921D1E2-8A85-4205-B4BA-D8967EE67093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E1405CD-34D5-476C-967F-ED56D5EF4FE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Adhoc Reimbursement Creation" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="80">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -86,180 +86,51 @@
     <t xml:space="preserve">Automation Payment Request </t>
   </si>
   <si>
-    <t>fieldTypeOfRequest__c</t>
-  </si>
-  <si>
     <t>Final</t>
   </si>
   <si>
-    <t>fieldBasisOfRequest__c</t>
-  </si>
-  <si>
     <t>Cash</t>
   </si>
   <si>
-    <t>fieldFederalAgencySF428__c</t>
-  </si>
-  <si>
     <t>TEST12345</t>
   </si>
   <si>
-    <t>fieldFederalAwardIdentifier__c</t>
-  </si>
-  <si>
-    <t>fieldPartialPaymentRequest__c</t>
-  </si>
-  <si>
-    <t>fieldFinancialAssistance__c</t>
-  </si>
-  <si>
-    <t>fieldPeriodStartDate__c</t>
-  </si>
-  <si>
-    <t>fieldPeriodEndDate__c</t>
-  </si>
-  <si>
-    <t>fieldRecipientOrganizationNameSF428__c</t>
-  </si>
-  <si>
     <t>TEST Organization</t>
   </si>
   <si>
-    <t>fieldStreet1SF428__c</t>
-  </si>
-  <si>
-    <t>fieldStreet2SF428__c</t>
-  </si>
-  <si>
     <t>Street 2</t>
   </si>
   <si>
-    <t>fieldCitySF428__c</t>
-  </si>
-  <si>
-    <t>fieldCountySF428__c</t>
-  </si>
-  <si>
     <t>NY</t>
   </si>
   <si>
-    <t>fieldStateSf428__c</t>
-  </si>
-  <si>
-    <t>fieldProvinceSF428__c</t>
-  </si>
-  <si>
-    <t>fieldCountrySF428__c</t>
-  </si>
-  <si>
     <t>USA: UNITED STATES</t>
   </si>
   <si>
-    <t>fieldZipPostalCodeSF428__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeOrganizationName__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeStreet1__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeStreet2__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeCity__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeCounty__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeState__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeProvince__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeCountry__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeZipCode__c</t>
-  </si>
-  <si>
-    <t>fieldPrograms__c</t>
-  </si>
-  <si>
-    <t>fieldFunctions__c</t>
-  </si>
-  <si>
-    <t>fieldActivities__c</t>
-  </si>
-  <si>
-    <t>fieldAcquiredDate__c</t>
-  </si>
-  <si>
-    <t>fieldEstimatedFederalCashOutlays__c</t>
-  </si>
-  <si>
-    <t>fieldEstimatedBalanceofFederalCashonHand__c</t>
-  </si>
-  <si>
-    <t>fieldAcknowledgementSF428__c</t>
-  </si>
-  <si>
     <t>checked</t>
   </si>
   <si>
-    <t>fieldSubmittedBySF428__c</t>
-  </si>
-  <si>
     <t>John Mathews</t>
   </si>
   <si>
-    <t>fieldSubmittedOn__c</t>
-  </si>
-  <si>
-    <t>fieldPrefix__c</t>
-  </si>
-  <si>
     <t>Mr.</t>
   </si>
   <si>
-    <t>fieldFirstNameSF428__c</t>
-  </si>
-  <si>
     <t>John</t>
   </si>
   <si>
-    <t>fieldMiddleNameSF428__c</t>
-  </si>
-  <si>
     <t>Andrew</t>
   </si>
   <si>
-    <t>fieldLastNameSF428__c</t>
-  </si>
-  <si>
     <t>Mathews</t>
   </si>
   <si>
-    <t>fieldSuffix__c</t>
-  </si>
-  <si>
     <t>Jr.</t>
   </si>
   <si>
-    <t>fieldTitleSF429__c</t>
-  </si>
-  <si>
     <t>Associate</t>
   </si>
   <si>
-    <t>fieldTelephone__c</t>
-  </si>
-  <si>
-    <t>fieldAgencyCommentsSF428__c</t>
-  </si>
-  <si>
     <t>Automation Test</t>
   </si>
   <si>
@@ -267,6 +138,138 @@
   </si>
   <si>
     <t>NY: New York</t>
+  </si>
+  <si>
+    <t>TypeOfRequest__c</t>
+  </si>
+  <si>
+    <t>BasisOfRequest__c</t>
+  </si>
+  <si>
+    <t>FederalAgencySF428__c</t>
+  </si>
+  <si>
+    <t>FederalAwardIdentifier__c</t>
+  </si>
+  <si>
+    <t>PartialPaymentRequest__c</t>
+  </si>
+  <si>
+    <t>FinancialAssistance__c</t>
+  </si>
+  <si>
+    <t>PeriodStartDate__c</t>
+  </si>
+  <si>
+    <t>PeriodEndDate__c</t>
+  </si>
+  <si>
+    <t>RecipientOrganizationNameSF428__c</t>
+  </si>
+  <si>
+    <t>Street1SF428__c</t>
+  </si>
+  <si>
+    <t>Street2SF428__c</t>
+  </si>
+  <si>
+    <t>CitySF428__c</t>
+  </si>
+  <si>
+    <t>CountySF428__c</t>
+  </si>
+  <si>
+    <t>StateSf428__c</t>
+  </si>
+  <si>
+    <t>ProvinceSF428__c</t>
+  </si>
+  <si>
+    <t>CountrySF428__c</t>
+  </si>
+  <si>
+    <t>ZipPostalCodeSF428__c</t>
+  </si>
+  <si>
+    <t>PayeeOrganizationName__c</t>
+  </si>
+  <si>
+    <t>PayeeStreet1__c</t>
+  </si>
+  <si>
+    <t>PayeeStreet2__c</t>
+  </si>
+  <si>
+    <t>PayeeCity__c</t>
+  </si>
+  <si>
+    <t>PayeeCounty__c</t>
+  </si>
+  <si>
+    <t>PayeeState__c</t>
+  </si>
+  <si>
+    <t>PayeeProvince__c</t>
+  </si>
+  <si>
+    <t>PayeeCountry__c</t>
+  </si>
+  <si>
+    <t>PayeeZipCode__c</t>
+  </si>
+  <si>
+    <t>Programs__c</t>
+  </si>
+  <si>
+    <t>Functions__c</t>
+  </si>
+  <si>
+    <t>Activities__c</t>
+  </si>
+  <si>
+    <t>AcquiredDate__c</t>
+  </si>
+  <si>
+    <t>EstimatedFederalCashOutlays__c</t>
+  </si>
+  <si>
+    <t>EstimatedBalanceofFederalCashonHand__c</t>
+  </si>
+  <si>
+    <t>AcknowledgementSF428__c</t>
+  </si>
+  <si>
+    <t>SubmittedBySF428__c</t>
+  </si>
+  <si>
+    <t>SubmittedOn__c</t>
+  </si>
+  <si>
+    <t>Prefix__c</t>
+  </si>
+  <si>
+    <t>FirstNameSF428__c</t>
+  </si>
+  <si>
+    <t>MiddleNameSF428__c</t>
+  </si>
+  <si>
+    <t>LastNameSF428__c</t>
+  </si>
+  <si>
+    <t>Suffix__c</t>
+  </si>
+  <si>
+    <t>TitleSF429__c</t>
+  </si>
+  <si>
+    <t>Telephone__c</t>
+  </si>
+  <si>
+    <t>AgencyCommentsSF428__c</t>
+  </si>
+  <si>
+    <t>FL: Florida</t>
   </si>
 </sst>
 </file>
@@ -637,13 +640,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -654,7 +657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -673,14 +676,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" customWidth="1"/>
+    <col min="1" max="1" width="10.26953125" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" customWidth="1"/>
+    <col min="3" max="3" width="23.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -691,7 +694,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -702,7 +705,7 @@
         <v>78954</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -713,7 +716,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -724,7 +727,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -743,13 +746,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="38.5703125" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" customWidth="1"/>
+    <col min="2" max="2" width="38.54296875" customWidth="1"/>
+    <col min="3" max="3" width="16.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -760,7 +763,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -771,7 +774,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -782,7 +785,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -802,13 +805,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -819,7 +822,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -830,7 +833,7 @@
         <v>6789678654</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -841,7 +844,7 @@
         <v>5678</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -852,7 +855,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -872,14 +875,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="12.26953125" customWidth="1"/>
+    <col min="2" max="2" width="20.81640625" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -890,7 +893,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -901,7 +904,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -920,13 +923,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A20A769E-7CDB-4643-B4E8-C9AF9D26E6C8}">
   <dimension ref="A1:C44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.1796875" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -937,477 +940,477 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C5" s="3">
         <v>123456789</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C6" s="3">
         <v>2121323223</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C7" s="3">
         <v>2121323223</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="C8" s="3">
         <v>365</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="C9" s="3">
         <v>730</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C11" s="3">
         <v>123</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
       <c r="B13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C20" s="3">
         <v>123</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>3</v>
       </c>
       <c r="B25" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="C28" s="3">
         <v>12345</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>3</v>
       </c>
       <c r="B29" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C29" s="3">
         <v>12345</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>3</v>
       </c>
       <c r="B30" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C30" s="3">
         <v>12345</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>3</v>
       </c>
       <c r="B31" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C31" s="3">
         <v>570</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C32" s="3">
         <v>12345</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>3</v>
       </c>
       <c r="B33" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C33" s="3">
         <v>12345</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C35" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C36" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>3</v>
       </c>
       <c r="B38" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>3</v>
       </c>
       <c r="B39" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>3</v>
       </c>
       <c r="B40" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>3</v>
       </c>
       <c r="B41" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>3</v>
       </c>
       <c r="B42" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>3</v>
       </c>
       <c r="B43" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C43" s="3">
         <v>2122342342</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/PaymentRequest_Field_Values.xlsx
+++ b/src/main/resources/PaymentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_New_Clone\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Demo Data Creation New\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB51AE2E-4E15-4AB1-A932-275CAA85AC51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD7C74B-67A5-434C-907D-5A4B0DA81BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Adhoc Reimbursement Creation" sheetId="1" r:id="rId1"/>
@@ -340,9 +340,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -380,7 +380,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -486,7 +486,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -628,7 +628,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -637,13 +637,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -654,7 +654,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -673,14 +673,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" customWidth="1"/>
+    <col min="1" max="1" width="10.26953125" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" customWidth="1"/>
+    <col min="3" max="3" width="23.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -691,7 +691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -702,7 +702,7 @@
         <v>78954</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -713,7 +713,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -724,7 +724,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -743,13 +743,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="34.28515625" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" customWidth="1"/>
+    <col min="2" max="2" width="34.26953125" customWidth="1"/>
+    <col min="3" max="3" width="16.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -760,7 +760,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -768,10 +768,10 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -782,7 +782,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -802,13 +802,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -819,7 +819,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -830,7 +830,7 @@
         <v>6789678654</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -841,7 +841,7 @@
         <v>5678</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -852,7 +852,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -872,14 +872,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="12.26953125" customWidth="1"/>
+    <col min="2" max="2" width="20.81640625" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -890,7 +890,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -901,7 +901,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -920,13 +920,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A20A769E-7CDB-4643-B4E8-C9AF9D26E6C8}">
   <dimension ref="A1:C44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.1796875" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -937,7 +937,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -948,7 +948,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -959,7 +959,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -970,7 +970,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -981,7 +981,7 @@
         <v>123456789</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -992,7 +992,7 @@
         <v>2121323223</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>2121323223</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1025,7 +1025,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1036,7 +1036,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1069,7 +1069,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1080,7 +1080,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -1113,7 +1113,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -1146,7 +1146,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -1157,7 +1157,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -1168,7 +1168,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -1179,7 +1179,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -1190,7 +1190,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -1201,7 +1201,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -1212,7 +1212,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>3</v>
       </c>
@@ -1234,7 +1234,7 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>3</v>
       </c>
@@ -1245,7 +1245,7 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>3</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>3</v>
       </c>
@@ -1267,7 +1267,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>3</v>
       </c>
@@ -1278,7 +1278,7 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>3</v>
       </c>
@@ -1289,7 +1289,7 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>3</v>
       </c>
@@ -1300,7 +1300,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>3</v>
       </c>
@@ -1311,7 +1311,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>3</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>3</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>3</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>3</v>
       </c>
@@ -1355,7 +1355,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>3</v>
       </c>
@@ -1366,7 +1366,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>3</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>3</v>
       </c>
@@ -1388,7 +1388,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>3</v>
       </c>
@@ -1399,7 +1399,7 @@
         <v>2122342342</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/PaymentRequest_Field_Values.xlsx
+++ b/src/main/resources/PaymentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Demo Data Creation 3.0\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E1405CD-34D5-476C-967F-ED56D5EF4FE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DC8E456-2494-4B5A-AF80-5F885D71D331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Adhoc Reimbursement Creation" sheetId="1" r:id="rId1"/>
@@ -771,7 +771,7 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>1000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
